--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130581350</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130581351</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130581356</v>
       </c>
       <c r="B6" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130581354</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>130581352</v>
       </c>
       <c r="B8" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130581350</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130581351</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130581356</v>
       </c>
       <c r="B6" t="n">
-        <v>57956</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130581354</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>130581352</v>
       </c>
       <c r="B8" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130581350</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130581351</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130581356</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>57966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130581354</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>130581352</v>
       </c>
       <c r="B8" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130581350</v>
       </c>
       <c r="B3" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130581351</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130581356</v>
       </c>
       <c r="B6" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130581354</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>130581352</v>
       </c>
       <c r="B8" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130581350</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130581351</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130581356</v>
       </c>
       <c r="B6" t="n">
-        <v>57967</v>
+        <v>57968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>130581354</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>130581352</v>
       </c>
       <c r="B8" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130581355</v>
       </c>
       <c r="B2" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130581349</v>
       </c>
       <c r="B5" t="n">
-        <v>91796</v>
+        <v>91804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37325-2022 artfynd.xlsx
+++ b/artfynd/A 37325-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130581355</v>
+        <v>130581352</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557450</v>
+        <v>557626</v>
       </c>
       <c r="R2" t="n">
-        <v>7189993</v>
+        <v>7190078</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -741,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -751,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130581350</v>
+        <v>130581351</v>
       </c>
       <c r="B3" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grantoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557376</v>
+        <v>557374</v>
       </c>
       <c r="R3" t="n">
-        <v>7190088</v>
+        <v>7190090</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130581351</v>
+        <v>130581354</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -925,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557374</v>
+        <v>557626</v>
       </c>
       <c r="R4" t="n">
-        <v>7190090</v>
+        <v>7190078</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -960,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -970,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,41 +996,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130581349</v>
+        <v>130581350</v>
       </c>
       <c r="B5" t="n">
-        <v>91828</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grantoppen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557380</v>
+        <v>557376</v>
       </c>
       <c r="R5" t="n">
-        <v>7190079</v>
+        <v>7190088</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,11 +1111,11 @@
         <v>130581356</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>58057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1213,220 +1221,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>130581354</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Grantoppen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>557626</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7190078</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130581352</v>
-      </c>
-      <c r="B8" t="n">
-        <v>80349</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Grantoppen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>557626</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7190078</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
